--- a/docs/video_manual/v1.6/exports/Report_Gatepass_Register.xlsx
+++ b/docs/video_manual/v1.6/exports/Report_Gatepass_Register.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Gatepass Register" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gatepass Register'!$A$4:$N$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gatepass Register'!$A$4:$N$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Dispatch date) · generated 18-10-2026 00:47 by Master Administrator</t>
+          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Dispatch date) · generated 21-10-2026 05:16 by Master Administrator</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -601,7 +601,7 @@
         <v>924</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         <v>30</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>500.01</v>
+        <v>500</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0</v>
@@ -644,10 +644,10 @@
         <v>0</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>500.01</v>
+        <v>500</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>500.01</v>
+        <v>500</v>
       </c>
       <c r="L6" s="6" t="n">
         <v>0</v>
@@ -663,7 +663,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46313</v>
+        <v>46316</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>600.01</v>
+        <v>550</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>0</v>
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>600.01</v>
+        <v>550</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>600.01</v>
+        <v>550</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>0</v>
@@ -766,45 +766,97 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DS/DM-KVR/2627/00002</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Transporter (long distance)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Shree Roadlines (Demo)</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>231</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>231</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>231</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Gone out</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>103</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>2456.02</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>2456.02</v>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>1532.02</v>
-      </c>
-      <c r="L9" s="10" t="n">
-        <v>924</v>
-      </c>
-      <c r="M9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>119</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>2637</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>2637</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>1482</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>1155</v>
+      </c>
+      <c r="M10" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" s="8" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N9"/>
+  <autoFilter ref="A4:N10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/video_manual/v1.6/exports/Report_Gatepass_Register.xlsx
+++ b/docs/video_manual/v1.6/exports/Report_Gatepass_Register.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd-mm-yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +39,11 @@
       <i val="1"/>
       <color rgb="005B6675"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -73,20 +78,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -481,84 +487,87 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Dispatch date) · generated 21-10-2026 05:16 by Master Administrator</t>
-        </is>
-      </c>
+          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Dispatch date) · generated 21-10-2026 14:47 by Master Administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Gatepass</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Transporter / auto</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Invoices</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Cases</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Freight</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Direct pickup</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Total charged</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Paid at dispatch</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>To be billed</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>LR missing</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>46316</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -576,31 +585,31 @@
           <t>Shree Roadlines (Demo)</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="7" t="n">
         <v>924</v>
       </c>
-      <c r="H5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="6" t="n">
+      <c r="H5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="7" t="n">
         <v>924</v>
       </c>
-      <c r="K5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="6" t="n">
+      <c r="K5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="7" t="n">
         <v>924</v>
       </c>
-      <c r="M5" s="5" t="n">
+      <c r="M5" s="6" t="n">
         <v>3</v>
       </c>
       <c r="N5" t="inlineStr">
@@ -610,7 +619,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>46316</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -628,31 +637,31 @@
           <t>Sharma Local Auto (Demo)</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="7" t="n">
         <v>500</v>
       </c>
-      <c r="H6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="6" t="n">
+      <c r="H6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="7" t="n">
         <v>500</v>
       </c>
-      <c r="K6" s="6" t="n">
+      <c r="K6" s="7" t="n">
         <v>500</v>
       </c>
-      <c r="L6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5" t="n">
+      <c r="L6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
@@ -662,7 +671,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="5" t="n">
         <v>46316</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -680,31 +689,31 @@
           <t>Ravi Tempo (Demo)</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="7" t="n">
         <v>432</v>
       </c>
-      <c r="H7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6" t="n">
+      <c r="H7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="7" t="n">
         <v>432</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="7" t="n">
         <v>432</v>
       </c>
-      <c r="L7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5" t="n">
+      <c r="L7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
@@ -714,7 +723,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="5" t="n">
         <v>46316</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -732,31 +741,31 @@
           <t>Kishore Mini Truck (Demo)</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="7" t="n">
         <v>550</v>
       </c>
-      <c r="H8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6" t="n">
+      <c r="H8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="7" t="n">
         <v>550</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="7" t="n">
         <v>550</v>
       </c>
-      <c r="L8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5" t="n">
+      <c r="L8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
@@ -766,7 +775,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="5" t="n">
         <v>46316</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -784,31 +793,31 @@
           <t>Shree Roadlines (Demo)</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="7" t="n">
         <v>231</v>
       </c>
-      <c r="H9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="6" t="n">
+      <c r="H9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="7" t="n">
         <v>231</v>
       </c>
-      <c r="K9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="6" t="n">
+      <c r="K9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7" t="n">
         <v>231</v>
       </c>
-      <c r="M9" s="5" t="n">
+      <c r="M9" s="6" t="n">
         <v>2</v>
       </c>
       <c r="N9" t="inlineStr">
@@ -818,42 +827,42 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="9" t="n">
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="10" t="n">
         <v>119</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="11" t="n">
         <v>2637</v>
       </c>
-      <c r="H10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="10" t="n">
+      <c r="H10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="11" t="n">
         <v>2637</v>
       </c>
-      <c r="K10" s="10" t="n">
+      <c r="K10" s="11" t="n">
         <v>1482</v>
       </c>
-      <c r="L10" s="10" t="n">
+      <c r="L10" s="11" t="n">
         <v>1155</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N10" s="8" t="n"/>
+      <c r="N10" s="9" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:N10"/>
